--- a/data/trans_orig/P37B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023</t>
+          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023 (tasa de respuesta: 97,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>415</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203984</t>
+          <t>204069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216874</t>
+          <t>216684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169834</t>
+          <t>169868</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178698</t>
+          <t>178512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>378266</t>
+          <t>378054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>393242</t>
+          <t>392957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78855</t>
+          <t>79878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125687</t>
+          <t>126467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86187</t>
+          <t>85223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116085</t>
+          <t>117332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174157</t>
+          <t>175309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228437</t>
+          <t>232599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166943</t>
+          <t>166897</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217329</t>
+          <t>217414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169946</t>
+          <t>168833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202229</t>
+          <t>202993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347368</t>
+          <t>345123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404745</t>
+          <t>408418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51144</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>23584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>63908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32980</t>
+          <t>33338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>163655</t>
+          <t>165131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187304</t>
+          <t>190004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>148465</t>
+          <t>149091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173689</t>
+          <t>173101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>320361</t>
+          <t>320194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>355624</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46493</t>
+          <t>45325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40654</t>
+          <t>40720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62331</t>
+          <t>61506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>70731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99443</t>
+          <t>100625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39788</t>
+          <t>38449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31623</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73627</t>
+          <t>73230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -2889,97 +2889,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2572</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3597</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2958</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136695</t>
+          <t>138941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>166863</t>
+          <t>168808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>266802</t>
+          <t>264701</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>309624</t>
+          <t>306086</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>412244</t>
+          <t>410222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>475727</t>
+          <t>471464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32318</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>837</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3571,97 +3571,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>81767</t>
+          <t>81802</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>98663</t>
+          <t>98620</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>75794</t>
+          <t>76850</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92216</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>162837</t>
+          <t>163939</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>187960</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45219</t>
+          <t>44301</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50254</t>
+          <t>50522</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73573</t>
+          <t>73352</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4253,97 +4253,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>544</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>177759</t>
+          <t>177123</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>190313</t>
+          <t>190199</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>143345</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>153406</t>
+          <t>153517</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>323531</t>
+          <t>324558</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>341063</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>44052</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>78628</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>42131</t>
+          <t>41544</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>64574</t>
+          <t>65844</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>91950</t>
+          <t>92910</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>132060</t>
+          <t>134484</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>334</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>55347</t>
+          <t>57484</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>265735</t>
+          <t>265462</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>317115</t>
+          <t>315722</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>284618</t>
+          <t>282926</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>315419</t>
+          <t>315127</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>562650</t>
+          <t>561339</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>623645</t>
+          <t>622718</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>57922</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>46089</t>
+          <t>44830</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>55005</t>
+          <t>56322</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>92930</t>
+          <t>94587</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>497766</t>
+          <t>499212</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>642431</t>
+          <t>668161</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>35891</t>
+          <t>37441</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>33773</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>151208</t>
+          <t>147101</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>596546</t>
+          <t>593354</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>343387</t>
+          <t>342065</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>372414</t>
+          <t>372202</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>377343</t>
+          <t>360550</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>956612</t>
+          <t>957062</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>31483</t>
+          <t>32647</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>38350</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>65160</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>225787</t>
+          <t>224683</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>937615</t>
+          <t>1024458</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>181719</t>
+          <t>184339</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>240820</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>433020</t>
+          <t>427884</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1522990</t>
+          <t>1330652</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>52446</t>
+          <t>50834</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>105609</t>
+          <t>104547</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>79494</t>
+          <t>78916</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,47 +6462,47 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>132178</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>103950</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>166601</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>132178</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>104605</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>166943</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1251894</t>
+          <t>1187141</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1884026</t>
+          <t>1884601</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1662265</t>
+          <t>1665455</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1759985</t>
+          <t>1756033</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2675225</t>
+          <t>2806577</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3598678</t>
+          <t>3599820</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>114282</t>
+          <t>116058</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>201449</t>
+          <t>201349</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>154141</t>
+          <t>152412</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>203696</t>
+          <t>203517</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>287247</t>
+          <t>284619</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>393770</t>
+          <t>390844</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>471</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>471</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>211930</t>
+          <t>218054</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204069</t>
+          <t>210722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216684</t>
+          <t>222517</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>175038</t>
+          <t>199975</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169868</t>
+          <t>194664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178512</t>
+          <t>203645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>386969</t>
+          <t>418029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>378054</t>
+          <t>409033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>392957</t>
+          <t>424099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>18071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>220972</t>
+          <t>227301</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220972</t>
+          <t>227301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>220972</t>
+          <t>227301</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>184139</t>
+          <t>210028</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>184139</t>
+          <t>210028</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>184139</t>
+          <t>210028</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>405112</t>
+          <t>437329</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>405112</t>
+          <t>437329</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>405112</t>
+          <t>437329</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>101754</t>
+          <t>105276</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79878</t>
+          <t>82949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126467</t>
+          <t>126595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100438</t>
+          <t>108127</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85223</t>
+          <t>91150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117332</t>
+          <t>124689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>202192</t>
+          <t>213403</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175309</t>
+          <t>188252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232599</t>
+          <t>242363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1633,67 +1633,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>15729</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9784</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23083</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>4,57%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14658</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9474</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>22443</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>22560</t>
+          <t>24947</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>35450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1746,22 +1746,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>192264</t>
+          <t>194591</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166897</t>
+          <t>171007</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217414</t>
+          <t>218946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>185879</t>
+          <t>197193</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168833</t>
+          <t>179824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202993</t>
+          <t>214195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>378142</t>
+          <t>391785</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>345123</t>
+          <t>361677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408418</t>
+          <t>421061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28896</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49659</t>
+          <t>48875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23584</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>44915</t>
+          <t>46259</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>33636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63908</t>
+          <t>65396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>332694</t>
+          <t>340867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>332694</t>
+          <t>340867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>332694</t>
+          <t>340867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>323239</t>
+          <t>343953</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>323239</t>
+          <t>343953</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>323239</t>
+          <t>343953</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>655933</t>
+          <t>684820</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>655933</t>
+          <t>684820</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>655933</t>
+          <t>684820</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>23885</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>19580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33338</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11012</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>177452</t>
+          <t>179594</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>165131</t>
+          <t>166781</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>190004</t>
+          <t>190579</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>161516</t>
+          <t>165355</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>149091</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173101</t>
+          <t>176517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>338969</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>320194</t>
+          <t>326493</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>355624</t>
+          <t>362454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>33318</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45325</t>
+          <t>44429</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>51414</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40720</t>
+          <t>41828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61506</t>
+          <t>63341</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>84864</t>
+          <t>84732</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70731</t>
+          <t>70806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100625</t>
+          <t>100867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>228409</t>
+          <t>229797</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>228409</t>
+          <t>229797</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>228409</t>
+          <t>229797</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>233261</t>
+          <t>240396</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>233261</t>
+          <t>240396</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>233261</t>
+          <t>240396</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>461670</t>
+          <t>470192</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>461670</t>
+          <t>470192</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>461670</t>
+          <t>470192</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38449</t>
+          <t>47287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26937</t>
+          <t>30371</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>52864</t>
+          <t>61767</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34093</t>
+          <t>48337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73230</t>
+          <t>78778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>571</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>571</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>19774</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>31538</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>153690</t>
+          <t>191186</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138941</t>
+          <t>170902</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168808</t>
+          <t>206166</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>286703</t>
+          <t>213751</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264701</t>
+          <t>199804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>306086</t>
+          <t>224153</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>440393</t>
+          <t>404938</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>410222</t>
+          <t>381586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>471464</t>
+          <t>426644</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>38242</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202460</t>
+          <t>253591</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>202460</t>
+          <t>253591</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>202460</t>
+          <t>253591</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>331092</t>
+          <t>265935</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>331092</t>
+          <t>265935</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>331092</t>
+          <t>265935</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>533552</t>
+          <t>519526</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>533552</t>
+          <t>519526</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>533552</t>
+          <t>519526</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>335</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>335</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>90775</t>
+          <t>109846</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>81802</t>
+          <t>99379</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>98620</t>
+          <t>117885</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>84960</t>
+          <t>93178</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>76850</t>
+          <t>83519</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>91749</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>175735</t>
+          <t>203025</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>163939</t>
+          <t>189266</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>187960</t>
+          <t>215881</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33732</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29219</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44301</t>
+          <t>50877</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>61337</t>
+          <t>69165</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50522</t>
+          <t>56784</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73352</t>
+          <t>82347</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>121506</t>
+          <t>144547</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>121506</t>
+          <t>144547</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>121506</t>
+          <t>144547</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>126401</t>
+          <t>140287</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>126401</t>
+          <t>140287</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>126401</t>
+          <t>140287</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>247907</t>
+          <t>284834</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>247907</t>
+          <t>284834</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>247907</t>
+          <t>284834</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>514</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4474,67 +4474,67 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>184841</t>
+          <t>185686</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>177123</t>
+          <t>177863</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>190199</t>
+          <t>190486</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>153370</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>147323</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>157659</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
           <t>93,56%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>149329</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>143345</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>153517</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>334170</t>
+          <t>339056</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>324558</t>
+          <t>330270</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>346354</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>197556</t>
+          <t>197905</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>197556</t>
+          <t>197905</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>197556</t>
+          <t>197905</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>159861</t>
+          <t>163921</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>159861</t>
+          <t>163921</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>159861</t>
+          <t>163921</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>357417</t>
+          <t>361826</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>357417</t>
+          <t>361826</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>357417</t>
+          <t>361826</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>58908</t>
+          <t>68290</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>49144</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>78628</t>
+          <t>86972</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>52731</t>
+          <t>68219</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>55540</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>65844</t>
+          <t>84768</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>111639</t>
+          <t>136509</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>92910</t>
+          <t>112173</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>134484</t>
+          <t>159613</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,22 +4965,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>25833</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,22 +5078,22 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>24505</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>57484</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>293747</t>
+          <t>333081</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>265462</t>
+          <t>307299</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>315722</t>
+          <t>357192</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>353531</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>282926</t>
+          <t>332510</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>315127</t>
+          <t>371401</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>594706</t>
+          <t>686612</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>561339</t>
+          <t>654511</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>622718</t>
+          <t>715260</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>44051</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>59224</t>
+          <t>64219</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>37394</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>71830</t>
+          <t>81446</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>94587</t>
+          <t>102167</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>411150</t>
+          <t>468476</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>411150</t>
+          <t>468476</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>411150</t>
+          <t>468476</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>402165</t>
+          <t>479522</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>402165</t>
+          <t>479522</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>402165</t>
+          <t>479522</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>813315</t>
+          <t>947998</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>813315</t>
+          <t>947998</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>813315</t>
+          <t>947998</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>253722</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>499212</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>261060</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>668161</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>736</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5637,77 +5637,77 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3861</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>5018</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t>0,51%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>3421</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>4163</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>20333</t>
+          <t>22626</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>37441</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>36983</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>371852</t>
+          <t>444417</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>147101</t>
+          <t>426862</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>593354</t>
+          <t>457752</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>360830</t>
+          <t>426896</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>342065</t>
+          <t>413903</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>372202</t>
+          <t>439281</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>732683</t>
+          <t>871313</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>360550</t>
+          <t>850799</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>957062</t>
+          <t>889347</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>19991</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>18538</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>44415</t>
+          <t>51824</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>65160</t>
+          <t>67523</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>663839</t>
+          <t>500043</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>663839</t>
+          <t>500043</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>663839</t>
+          <t>500043</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>412903</t>
+          <t>482080</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>412903</t>
+          <t>482080</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>412903</t>
+          <t>482080</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1076742</t>
+          <t>982123</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1076742</t>
+          <t>982123</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1076742</t>
+          <t>982123</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>456159</t>
+          <t>233320</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>224683</t>
+          <t>198641</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1024458</t>
+          <t>271654</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>211556</t>
+          <t>242703</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>184339</t>
+          <t>216045</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>240820</t>
+          <t>270603</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>667715</t>
+          <t>476023</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>427884</t>
+          <t>430494</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1330652</t>
+          <t>521633</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>29767</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14638</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>49859</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>74068</t>
+          <t>84200</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>50834</t>
+          <t>67036</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>104547</t>
+          <t>106136</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>59756</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>47451</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>78916</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,27 +6477,27 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>132178</t>
+          <t>143955</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>103950</t>
+          <t>121775</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>171654</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1676552</t>
+          <t>1856456</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1187141</t>
+          <t>1810686</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1884601</t>
+          <t>1898698</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1705215</t>
+          <t>1803249</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1665455</t>
+          <t>1764351</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1756033</t>
+          <t>1837126</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>3381767</t>
+          <t>3659705</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2806577</t>
+          <t>3601096</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3599820</t>
+          <t>3717623</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>165617</t>
+          <t>175029</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>116058</t>
+          <t>150217</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>201349</t>
+          <t>204818</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>178385</t>
+          <t>198524</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>152412</t>
+          <t>177864</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>203517</t>
+          <t>225848</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>344002</t>
+          <t>373553</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>284619</t>
+          <t>337173</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>390844</t>
+          <t>410293</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2378587</t>
+          <t>2362527</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>2173061</t>
+          <t>2326121</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>4551648</t>
+          <t>4688648</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
